--- a/zawodnicy_eg.xlsx
+++ b/zawodnicy_eg.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[Katar] Eithad Al-Gharafa</t>
+          <t>[Katar] Al-Gharafa II</t>
         </is>
       </c>
     </row>
